--- a/Unity/Assets/Config/Excel/BattleSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BattleSceneConfig.xlsx
@@ -41,7 +41,7 @@
     <t>AssetPath</t>
   </si>
   <si>
-    <t>int</t>
+    <t>long</t>
   </si>
   <si>
     <t>string</t>
@@ -735,13 +735,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
